--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1113,7 +1113,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1319,7 +1319,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
